--- a/data-manipulation-scripts/sheets-cleanup/sheets/ROLETE EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ROLETE EMBREAGEM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>ROLETE EMBREAGEM PRIMARIA TRILHA NEO115 2010 A 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1054,9 @@
     </row>
     <row r="34">
       <c r="A34" s="9"/>
-      <c r="B34" s="10"/>
+      <c r="B34" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
     </row>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/ROLETE EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ROLETE EMBREAGEM.xlsx
@@ -167,7 +167,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -440,7 +440,9 @@
       <c r="C2" s="4">
         <v>4.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>45.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -474,7 +476,9 @@
       <c r="C3" s="4">
         <v>7.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>45.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -724,7 +728,9 @@
       <c r="C10" s="7">
         <v>3.0</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5">
+        <v>45.0</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -794,7 +800,9 @@
       <c r="C12" s="7">
         <v>2.0</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="5">
+        <v>45.0</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -864,7 +872,9 @@
       <c r="C14" s="7">
         <v>1.0</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="5">
+        <v>45.0</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
